--- a/Archived_HE_Data/hedata_2026-09-15.xlsx
+++ b/Archived_HE_Data/hedata_2026-09-15.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1623" uniqueCount="911">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1635" uniqueCount="920">
   <si>
     <t>Title</t>
   </si>
@@ -2269,12 +2269,12 @@
     <t>1115 N Roberts St, Helena, MT 59601, USA</t>
   </si>
   <si>
+    <t>https://www.schooljobs.com/careers/ummissoula/jobs/4993102/adjunct-nursing-clinical-instructor-crrn</t>
+  </si>
+  <si>
     <t>https://www.schooljobs.com/careers/ummissoula/jobs/4694471/adjunct-nursing-clinical-instructor-crrn</t>
   </si>
   <si>
-    <t>https://www.schooljobs.com/careers/ummissoula/jobs/4993102/adjunct-nursing-clinical-instructor-crrn</t>
-  </si>
-  <si>
     <t>Administrartive Associate III</t>
   </si>
   <si>
@@ -2531,6 +2531,33 @@
   </si>
   <si>
     <t>Special Event Team Members- Part-time</t>
+  </si>
+  <si>
+    <t>Admissions Counselor</t>
+  </si>
+  <si>
+    <t>Admissions</t>
+  </si>
+  <si>
+    <t>Rocky Mountain College</t>
+  </si>
+  <si>
+    <t>https://rocky.edu/employment/opportunities/admissions-counselor/</t>
+  </si>
+  <si>
+    <t>Head Bears Cheer Coach</t>
+  </si>
+  <si>
+    <t>https://rocky.edu/employment/opportunities/head-bears-cheer-coach/</t>
+  </si>
+  <si>
+    <t>Airframe &amp; Powerplant Certified Mechanic with (I/ A) Inspection Authorization</t>
+  </si>
+  <si>
+    <t>Aviation</t>
+  </si>
+  <si>
+    <t>https://rocky.edu/employment/opportunities/airframe-powerplant-certified-mechanic-with-i-a-inspection-authorization/</t>
   </si>
   <si>
     <t>Open Rank Professor of Counseling</t>
@@ -3093,7 +3120,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F351"/>
+  <dimension ref="A1:F354"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="6" max="6" width="20.7109375" style="1" customWidth="1"/>
@@ -9052,14 +9079,14 @@
       <c r="A313" t="s">
         <v>839</v>
       </c>
-      <c r="C313" t="s">
-        <v>91</v>
+      <c r="B313" t="s">
+        <v>840</v>
       </c>
       <c r="D313" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E313" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="F313" s="1">
         <v>46280</v>
@@ -9067,16 +9094,13 @@
     </row>
     <row r="314" spans="1:6">
       <c r="A314" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B314" t="s">
-        <v>843</v>
-      </c>
-      <c r="C314" t="s">
-        <v>225</v>
+        <v>84</v>
       </c>
       <c r="D314" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E314" t="s">
         <v>844</v>
@@ -9087,19 +9111,16 @@
     </row>
     <row r="315" spans="1:6">
       <c r="A315" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="B315" t="s">
-        <v>843</v>
-      </c>
-      <c r="C315" t="s">
-        <v>273</v>
+        <v>846</v>
       </c>
       <c r="D315" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="E315" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="F315" s="1">
         <v>46280</v>
@@ -9107,19 +9128,16 @@
     </row>
     <row r="316" spans="1:6">
       <c r="A316" t="s">
-        <v>846</v>
-      </c>
-      <c r="B316" t="s">
-        <v>843</v>
+        <v>848</v>
       </c>
       <c r="C316" t="s">
-        <v>288</v>
+        <v>91</v>
       </c>
       <c r="D316" t="s">
-        <v>840</v>
+        <v>849</v>
       </c>
       <c r="E316" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="F316" s="1">
         <v>46280</v>
@@ -9127,16 +9145,19 @@
     </row>
     <row r="317" spans="1:6">
       <c r="A317" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="B317" t="s">
+        <v>852</v>
+      </c>
+      <c r="C317" t="s">
+        <v>225</v>
+      </c>
+      <c r="D317" t="s">
         <v>849</v>
       </c>
-      <c r="D317" t="s">
-        <v>850</v>
-      </c>
       <c r="E317" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="F317" s="1">
         <v>46280</v>
@@ -9144,16 +9165,19 @@
     </row>
     <row r="318" spans="1:6">
       <c r="A318" t="s">
+        <v>834</v>
+      </c>
+      <c r="B318" t="s">
         <v>852</v>
       </c>
-      <c r="B318" t="s">
+      <c r="C318" t="s">
+        <v>273</v>
+      </c>
+      <c r="D318" t="s">
         <v>849</v>
       </c>
-      <c r="D318" t="s">
-        <v>850</v>
-      </c>
       <c r="E318" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="F318" s="1">
         <v>46280</v>
@@ -9161,16 +9185,19 @@
     </row>
     <row r="319" spans="1:6">
       <c r="A319" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="B319" t="s">
+        <v>852</v>
+      </c>
+      <c r="C319" t="s">
+        <v>288</v>
+      </c>
+      <c r="D319" t="s">
         <v>849</v>
       </c>
-      <c r="D319" t="s">
-        <v>850</v>
-      </c>
       <c r="E319" t="s">
-        <v>851</v>
+        <v>856</v>
       </c>
       <c r="F319" s="1">
         <v>46280</v>
@@ -9178,16 +9205,16 @@
     </row>
     <row r="320" spans="1:6">
       <c r="A320" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="B320" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D320" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E320" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F320" s="1">
         <v>46280</v>
@@ -9195,16 +9222,16 @@
     </row>
     <row r="321" spans="1:6">
       <c r="A321" t="s">
-        <v>855</v>
+        <v>861</v>
       </c>
       <c r="B321" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D321" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E321" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F321" s="1">
         <v>46280</v>
@@ -9212,16 +9239,16 @@
     </row>
     <row r="322" spans="1:6">
       <c r="A322" t="s">
-        <v>856</v>
+        <v>862</v>
       </c>
       <c r="B322" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D322" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E322" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F322" s="1">
         <v>46280</v>
@@ -9229,16 +9256,16 @@
     </row>
     <row r="323" spans="1:6">
       <c r="A323" t="s">
-        <v>857</v>
+        <v>863</v>
       </c>
       <c r="B323" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D323" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E323" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F323" s="1">
         <v>46280</v>
@@ -9246,16 +9273,16 @@
     </row>
     <row r="324" spans="1:6">
       <c r="A324" t="s">
+        <v>864</v>
+      </c>
+      <c r="B324" t="s">
         <v>858</v>
       </c>
-      <c r="B324" t="s">
-        <v>849</v>
-      </c>
       <c r="D324" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E324" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F324" s="1">
         <v>46280</v>
@@ -9263,16 +9290,16 @@
     </row>
     <row r="325" spans="1:6">
       <c r="A325" t="s">
+        <v>865</v>
+      </c>
+      <c r="B325" t="s">
+        <v>858</v>
+      </c>
+      <c r="D325" t="s">
         <v>859</v>
       </c>
-      <c r="B325" t="s">
-        <v>849</v>
-      </c>
-      <c r="D325" t="s">
-        <v>850</v>
-      </c>
       <c r="E325" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F325" s="1">
         <v>46280</v>
@@ -9280,16 +9307,16 @@
     </row>
     <row r="326" spans="1:6">
       <c r="A326" t="s">
+        <v>866</v>
+      </c>
+      <c r="B326" t="s">
+        <v>858</v>
+      </c>
+      <c r="D326" t="s">
+        <v>859</v>
+      </c>
+      <c r="E326" t="s">
         <v>860</v>
-      </c>
-      <c r="B326" t="s">
-        <v>849</v>
-      </c>
-      <c r="D326" t="s">
-        <v>850</v>
-      </c>
-      <c r="E326" t="s">
-        <v>851</v>
       </c>
       <c r="F326" s="1">
         <v>46280</v>
@@ -9297,16 +9324,16 @@
     </row>
     <row r="327" spans="1:6">
       <c r="A327" t="s">
-        <v>861</v>
+        <v>867</v>
       </c>
       <c r="B327" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D327" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E327" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F327" s="1">
         <v>46280</v>
@@ -9314,16 +9341,16 @@
     </row>
     <row r="328" spans="1:6">
       <c r="A328" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="B328" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D328" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E328" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F328" s="1">
         <v>46280</v>
@@ -9331,16 +9358,16 @@
     </row>
     <row r="329" spans="1:6">
       <c r="A329" t="s">
-        <v>863</v>
+        <v>869</v>
       </c>
       <c r="B329" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D329" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E329" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F329" s="1">
         <v>46280</v>
@@ -9348,16 +9375,16 @@
     </row>
     <row r="330" spans="1:6">
       <c r="A330" t="s">
-        <v>864</v>
+        <v>870</v>
       </c>
       <c r="B330" t="s">
-        <v>849</v>
+        <v>858</v>
       </c>
       <c r="D330" t="s">
-        <v>850</v>
+        <v>859</v>
       </c>
       <c r="E330" t="s">
-        <v>851</v>
+        <v>860</v>
       </c>
       <c r="F330" s="1">
         <v>46280</v>
@@ -9365,16 +9392,16 @@
     </row>
     <row r="331" spans="1:6">
       <c r="A331" t="s">
-        <v>865</v>
+        <v>871</v>
       </c>
       <c r="B331" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="D331" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="E331" t="s">
-        <v>868</v>
+        <v>860</v>
       </c>
       <c r="F331" s="1">
         <v>46280</v>
@@ -9382,16 +9409,16 @@
     </row>
     <row r="332" spans="1:6">
       <c r="A332" t="s">
-        <v>869</v>
+        <v>872</v>
       </c>
       <c r="B332" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="D332" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="E332" t="s">
-        <v>870</v>
+        <v>860</v>
       </c>
       <c r="F332" s="1">
         <v>46280</v>
@@ -9399,16 +9426,16 @@
     </row>
     <row r="333" spans="1:6">
       <c r="A333" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="B333" t="s">
-        <v>866</v>
+        <v>858</v>
       </c>
       <c r="D333" t="s">
-        <v>867</v>
+        <v>859</v>
       </c>
       <c r="E333" t="s">
-        <v>872</v>
+        <v>860</v>
       </c>
       <c r="F333" s="1">
         <v>46280</v>
@@ -9416,16 +9443,16 @@
     </row>
     <row r="334" spans="1:6">
       <c r="A334" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B334" t="s">
-        <v>866</v>
+        <v>875</v>
       </c>
       <c r="D334" t="s">
-        <v>867</v>
+        <v>876</v>
       </c>
       <c r="E334" t="s">
-        <v>874</v>
+        <v>877</v>
       </c>
       <c r="F334" s="1">
         <v>46280</v>
@@ -9433,16 +9460,16 @@
     </row>
     <row r="335" spans="1:6">
       <c r="A335" t="s">
+        <v>878</v>
+      </c>
+      <c r="B335" t="s">
         <v>875</v>
       </c>
-      <c r="B335" t="s">
+      <c r="D335" t="s">
         <v>876</v>
       </c>
-      <c r="D335" t="s">
-        <v>877</v>
-      </c>
       <c r="E335" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="F335" s="1">
         <v>46280</v>
@@ -9450,16 +9477,16 @@
     </row>
     <row r="336" spans="1:6">
       <c r="A336" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B336" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="D336" t="s">
+        <v>876</v>
+      </c>
+      <c r="E336" t="s">
         <v>881</v>
-      </c>
-      <c r="E336" t="s">
-        <v>882</v>
       </c>
       <c r="F336" s="1">
         <v>46280</v>
@@ -9467,16 +9494,16 @@
     </row>
     <row r="337" spans="1:6">
       <c r="A337" t="s">
+        <v>882</v>
+      </c>
+      <c r="B337" t="s">
+        <v>875</v>
+      </c>
+      <c r="D337" t="s">
+        <v>876</v>
+      </c>
+      <c r="E337" t="s">
         <v>883</v>
-      </c>
-      <c r="B337" t="s">
-        <v>880</v>
-      </c>
-      <c r="D337" t="s">
-        <v>881</v>
-      </c>
-      <c r="E337" t="s">
-        <v>882</v>
       </c>
       <c r="F337" s="1">
         <v>46280</v>
@@ -9487,13 +9514,13 @@
         <v>884</v>
       </c>
       <c r="B338" t="s">
-        <v>880</v>
+        <v>885</v>
       </c>
       <c r="D338" t="s">
-        <v>881</v>
+        <v>886</v>
       </c>
       <c r="E338" t="s">
-        <v>882</v>
+        <v>887</v>
       </c>
       <c r="F338" s="1">
         <v>46280</v>
@@ -9501,16 +9528,16 @@
     </row>
     <row r="339" spans="1:6">
       <c r="A339" t="s">
-        <v>885</v>
+        <v>888</v>
       </c>
       <c r="B339" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="D339" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E339" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="F339" s="1">
         <v>46280</v>
@@ -9518,16 +9545,16 @@
     </row>
     <row r="340" spans="1:6">
       <c r="A340" t="s">
-        <v>886</v>
+        <v>892</v>
       </c>
       <c r="B340" t="s">
-        <v>880</v>
+        <v>889</v>
       </c>
       <c r="D340" t="s">
-        <v>881</v>
+        <v>890</v>
       </c>
       <c r="E340" t="s">
-        <v>882</v>
+        <v>891</v>
       </c>
       <c r="F340" s="1">
         <v>46280</v>
@@ -9535,16 +9562,16 @@
     </row>
     <row r="341" spans="1:6">
       <c r="A341" t="s">
-        <v>887</v>
+        <v>893</v>
       </c>
       <c r="B341" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D341" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E341" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="F341" s="1">
         <v>46280</v>
@@ -9552,16 +9579,16 @@
     </row>
     <row r="342" spans="1:6">
       <c r="A342" t="s">
+        <v>894</v>
+      </c>
+      <c r="B342" t="s">
+        <v>889</v>
+      </c>
+      <c r="D342" t="s">
+        <v>890</v>
+      </c>
+      <c r="E342" t="s">
         <v>891</v>
-      </c>
-      <c r="B342" t="s">
-        <v>888</v>
-      </c>
-      <c r="D342" t="s">
-        <v>889</v>
-      </c>
-      <c r="E342" t="s">
-        <v>892</v>
       </c>
       <c r="F342" s="1">
         <v>46280</v>
@@ -9569,16 +9596,16 @@
     </row>
     <row r="343" spans="1:6">
       <c r="A343" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="B343" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D343" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="E343" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="F343" s="1">
         <v>46280</v>
@@ -9586,16 +9613,16 @@
     </row>
     <row r="344" spans="1:6">
       <c r="A344" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B344" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D344" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E344" t="s">
-        <v>896</v>
+        <v>899</v>
       </c>
       <c r="F344" s="1">
         <v>46280</v>
@@ -9603,16 +9630,16 @@
     </row>
     <row r="345" spans="1:6">
       <c r="A345" t="s">
+        <v>900</v>
+      </c>
+      <c r="B345" t="s">
         <v>897</v>
       </c>
-      <c r="B345" t="s">
-        <v>888</v>
-      </c>
       <c r="D345" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E345" t="s">
-        <v>898</v>
+        <v>901</v>
       </c>
       <c r="F345" s="1">
         <v>46280</v>
@@ -9620,16 +9647,16 @@
     </row>
     <row r="346" spans="1:6">
       <c r="A346" t="s">
-        <v>899</v>
+        <v>902</v>
       </c>
       <c r="B346" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D346" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E346" t="s">
-        <v>900</v>
+        <v>903</v>
       </c>
       <c r="F346" s="1">
         <v>46280</v>
@@ -9637,16 +9664,16 @@
     </row>
     <row r="347" spans="1:6">
       <c r="A347" t="s">
-        <v>901</v>
+        <v>904</v>
       </c>
       <c r="B347" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D347" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E347" t="s">
-        <v>902</v>
+        <v>905</v>
       </c>
       <c r="F347" s="1">
         <v>46280</v>
@@ -9654,16 +9681,16 @@
     </row>
     <row r="348" spans="1:6">
       <c r="A348" t="s">
-        <v>903</v>
+        <v>906</v>
       </c>
       <c r="B348" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D348" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E348" t="s">
-        <v>904</v>
+        <v>907</v>
       </c>
       <c r="F348" s="1">
         <v>46280</v>
@@ -9671,16 +9698,16 @@
     </row>
     <row r="349" spans="1:6">
       <c r="A349" t="s">
-        <v>905</v>
+        <v>908</v>
       </c>
       <c r="B349" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D349" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E349" t="s">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="F349" s="1">
         <v>46280</v>
@@ -9688,16 +9715,16 @@
     </row>
     <row r="350" spans="1:6">
       <c r="A350" t="s">
-        <v>907</v>
+        <v>910</v>
       </c>
       <c r="B350" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D350" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E350" t="s">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="F350" s="1">
         <v>46280</v>
@@ -9705,18 +9732,69 @@
     </row>
     <row r="351" spans="1:6">
       <c r="A351" t="s">
-        <v>909</v>
+        <v>912</v>
       </c>
       <c r="B351" t="s">
-        <v>888</v>
+        <v>897</v>
       </c>
       <c r="D351" t="s">
-        <v>889</v>
+        <v>898</v>
       </c>
       <c r="E351" t="s">
-        <v>910</v>
+        <v>913</v>
       </c>
       <c r="F351" s="1">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
+      <c r="A352" t="s">
+        <v>914</v>
+      </c>
+      <c r="B352" t="s">
+        <v>897</v>
+      </c>
+      <c r="D352" t="s">
+        <v>898</v>
+      </c>
+      <c r="E352" t="s">
+        <v>915</v>
+      </c>
+      <c r="F352" s="1">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
+      <c r="A353" t="s">
+        <v>916</v>
+      </c>
+      <c r="B353" t="s">
+        <v>897</v>
+      </c>
+      <c r="D353" t="s">
+        <v>898</v>
+      </c>
+      <c r="E353" t="s">
+        <v>917</v>
+      </c>
+      <c r="F353" s="1">
+        <v>46280</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
+      <c r="A354" t="s">
+        <v>918</v>
+      </c>
+      <c r="B354" t="s">
+        <v>897</v>
+      </c>
+      <c r="D354" t="s">
+        <v>898</v>
+      </c>
+      <c r="E354" t="s">
+        <v>919</v>
+      </c>
+      <c r="F354" s="1">
         <v>46280</v>
       </c>
     </row>
